--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1093,50 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127126740</v>
+        <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>80143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595917</v>
+        <v>595935</v>
       </c>
       <c r="R6" t="n">
-        <v>6986144</v>
+        <v>6986169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1302,45 +1297,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127127032</v>
+        <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>80112</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595935</v>
+        <v>595917</v>
       </c>
       <c r="R8" t="n">
-        <v>6986169</v>
+        <v>6986144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,38 +1399,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127125963</v>
+        <v>127126832</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1439,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595866</v>
+        <v>595893</v>
       </c>
       <c r="R9" t="n">
-        <v>6986273</v>
+        <v>6986174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1474,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,49 +1500,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126832</v>
+        <v>127126974</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595893</v>
+        <v>595916</v>
       </c>
       <c r="R10" t="n">
-        <v>6986174</v>
+        <v>6986192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126974</v>
+        <v>127125963</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,34 +1608,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595916</v>
+        <v>595866</v>
       </c>
       <c r="R11" t="n">
-        <v>6986192</v>
+        <v>6986273</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,6 +1673,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,7 +1707,7 @@
         <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97242</v>
+        <v>97317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>127126184</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>127127137</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>127127199</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,49 +2387,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124915</v>
+        <v>127127074</v>
       </c>
       <c r="B19" t="n">
-        <v>98278</v>
+        <v>80114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595778</v>
+        <v>595931</v>
       </c>
       <c r="R19" t="n">
-        <v>6986242</v>
+        <v>6986212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,45 +2484,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127127074</v>
+        <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>80083</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595931</v>
+        <v>595778</v>
       </c>
       <c r="R20" t="n">
-        <v>6986212</v>
+        <v>6986242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R3" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R4" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,45 +1093,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127127032</v>
+        <v>127126740</v>
       </c>
       <c r="B6" t="n">
-        <v>80143</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595935</v>
+        <v>595917</v>
       </c>
       <c r="R6" t="n">
-        <v>6986169</v>
+        <v>6986144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,50 +1195,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127126520</v>
+        <v>127127032</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595819</v>
+        <v>595935</v>
       </c>
       <c r="R7" t="n">
-        <v>6986191</v>
+        <v>6986169</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,27 +1303,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R8" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,49 +1399,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126832</v>
+        <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595893</v>
+        <v>595916</v>
       </c>
       <c r="R9" t="n">
-        <v>6986174</v>
+        <v>6986192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126974</v>
+        <v>127125963</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595916</v>
+        <v>595866</v>
       </c>
       <c r="R10" t="n">
-        <v>6986192</v>
+        <v>6986273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,38 +1603,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125963</v>
+        <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595866</v>
+        <v>595893</v>
       </c>
       <c r="R11" t="n">
-        <v>6986273</v>
+        <v>6986174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,7 +1707,7 @@
         <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97317</v>
+        <v>97323</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127126184</v>
+        <v>127127199</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595844</v>
+        <v>595911</v>
       </c>
       <c r="R16" t="n">
-        <v>6986247</v>
+        <v>6986287</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127137</v>
+        <v>127126184</v>
       </c>
       <c r="B17" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595925</v>
+        <v>595844</v>
       </c>
       <c r="R17" t="n">
-        <v>6986226</v>
+        <v>6986247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127199</v>
+        <v>127127137</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595911</v>
+        <v>595925</v>
       </c>
       <c r="R18" t="n">
-        <v>6986287</v>
+        <v>6986226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
         <v>127127074</v>
       </c>
       <c r="B19" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R3" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R4" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,50 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127126740</v>
+        <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595917</v>
+        <v>595935</v>
       </c>
       <c r="R6" t="n">
-        <v>6986144</v>
+        <v>6986169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,45 +1190,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127127032</v>
+        <v>127126520</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595935</v>
+        <v>595819</v>
       </c>
       <c r="R7" t="n">
-        <v>6986169</v>
+        <v>6986191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126520</v>
+        <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,27 +1308,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595819</v>
+        <v>595917</v>
       </c>
       <c r="R8" t="n">
-        <v>6986191</v>
+        <v>6986144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,45 +1399,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126974</v>
+        <v>127126832</v>
       </c>
       <c r="B9" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595916</v>
+        <v>595893</v>
       </c>
       <c r="R9" t="n">
-        <v>6986192</v>
+        <v>6986174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127125963</v>
+        <v>127126974</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,39 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595866</v>
+        <v>595916</v>
       </c>
       <c r="R10" t="n">
-        <v>6986273</v>
+        <v>6986192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,37 +1597,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126832</v>
+        <v>127125963</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595893</v>
+        <v>595866</v>
       </c>
       <c r="R11" t="n">
-        <v>6986174</v>
+        <v>6986273</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,6 +1673,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,45 +1704,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R12" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,49 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R13" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127127199</v>
+        <v>127126184</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595911</v>
+        <v>595844</v>
       </c>
       <c r="R16" t="n">
-        <v>6986287</v>
+        <v>6986247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127126184</v>
+        <v>127127137</v>
       </c>
       <c r="B17" t="n">
         <v>80117</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595844</v>
+        <v>595925</v>
       </c>
       <c r="R17" t="n">
-        <v>6986247</v>
+        <v>6986226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127137</v>
+        <v>127127199</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595925</v>
+        <v>595911</v>
       </c>
       <c r="R18" t="n">
-        <v>6986226</v>
+        <v>6986287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -1399,37 +1399,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126832</v>
+        <v>127125963</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1438,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595893</v>
+        <v>595866</v>
       </c>
       <c r="R9" t="n">
-        <v>6986174</v>
+        <v>6986273</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,45 +1506,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126974</v>
+        <v>127126832</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595916</v>
+        <v>595893</v>
       </c>
       <c r="R10" t="n">
-        <v>6986192</v>
+        <v>6986174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125963</v>
+        <v>127126974</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,39 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595866</v>
+        <v>595916</v>
       </c>
       <c r="R11" t="n">
-        <v>6986273</v>
+        <v>6986192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,49 +1704,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R12" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,45 +1801,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R13" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -1506,49 +1506,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126832</v>
+        <v>127126974</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595893</v>
+        <v>595916</v>
       </c>
       <c r="R10" t="n">
-        <v>6986174</v>
+        <v>6986192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,45 +1603,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126974</v>
+        <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595916</v>
+        <v>595893</v>
       </c>
       <c r="R11" t="n">
-        <v>6986192</v>
+        <v>6986174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,45 +1704,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R12" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,49 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R13" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97323</v>
+        <v>97324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127125963</v>
+        <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,39 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595866</v>
+        <v>595916</v>
       </c>
       <c r="R9" t="n">
-        <v>6986273</v>
+        <v>6986192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126974</v>
+        <v>127125963</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595916</v>
+        <v>595866</v>
       </c>
       <c r="R10" t="n">
-        <v>6986192</v>
+        <v>6986273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2692,6 +2692,693 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127428158</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>595853</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6986240</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127428280</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595878</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6986233</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127428596</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>595930</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6986250</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127428192</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91900</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>760</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>595852</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6986240</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127428567</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595920</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6986240</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127428437</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595915</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6986247</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127428774</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>595886</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6986311</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R3" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R4" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,45 +1093,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127127032</v>
+        <v>127126740</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595935</v>
+        <v>595917</v>
       </c>
       <c r="R6" t="n">
-        <v>6986169</v>
+        <v>6986144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,50 +1195,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127126520</v>
+        <v>127127032</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595819</v>
+        <v>595935</v>
       </c>
       <c r="R7" t="n">
-        <v>6986191</v>
+        <v>6986169</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,27 +1303,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R8" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R22" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>80117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R23" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>91900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R24" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B25" t="n">
-        <v>91900</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R25" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R3" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R4" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1704,49 +1704,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R12" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,45 +1801,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R13" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R3" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R4" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1704,45 +1704,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R12" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,49 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R13" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3082,49 +3082,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R26" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3183,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R27" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127126594</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127126904</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,27 +1104,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R6" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,45 +1200,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127127032</v>
+        <v>127126740</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595935</v>
+        <v>595917</v>
       </c>
       <c r="R7" t="n">
-        <v>6986169</v>
+        <v>6986144</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,50 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126520</v>
+        <v>127127032</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595819</v>
+        <v>595935</v>
       </c>
       <c r="R8" t="n">
-        <v>6986191</v>
+        <v>6986169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126974</v>
+        <v>127125963</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,34 +1410,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595916</v>
+        <v>595866</v>
       </c>
       <c r="R9" t="n">
-        <v>6986192</v>
+        <v>6986273</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,38 +1506,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127125963</v>
+        <v>127126832</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1536,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595866</v>
+        <v>595893</v>
       </c>
       <c r="R10" t="n">
-        <v>6986273</v>
+        <v>6986174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1581,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,49 +1607,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126832</v>
+        <v>127126974</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595893</v>
+        <v>595916</v>
       </c>
       <c r="R11" t="n">
-        <v>6986174</v>
+        <v>6986192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,49 +1704,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R12" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,45 +1801,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R13" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97324</v>
+        <v>97328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>127126184</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>127127137</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>127127199</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>127127074</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>127126106</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>80121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R22" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B23" t="n">
-        <v>80117</v>
+        <v>91330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R23" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2891,7 +2891,7 @@
         <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>127428596</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,45 +3082,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R26" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3179,49 +3183,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R27" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R3" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R4" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,50 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127126520</v>
+        <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595819</v>
+        <v>595935</v>
       </c>
       <c r="R6" t="n">
-        <v>6986191</v>
+        <v>6986169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,27 +1201,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R7" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,45 +1297,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127127032</v>
+        <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>57821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595935</v>
+        <v>595917</v>
       </c>
       <c r="R8" t="n">
-        <v>6986169</v>
+        <v>6986144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127125963</v>
+        <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,39 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595866</v>
+        <v>595916</v>
       </c>
       <c r="R9" t="n">
-        <v>6986273</v>
+        <v>6986192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,37 +1496,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126832</v>
+        <v>127125963</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1545,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595893</v>
+        <v>595866</v>
       </c>
       <c r="R10" t="n">
-        <v>6986174</v>
+        <v>6986273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,45 +1603,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126974</v>
+        <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595916</v>
+        <v>595893</v>
       </c>
       <c r="R11" t="n">
-        <v>6986192</v>
+        <v>6986174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R22" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R23" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B24" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R24" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>91904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R25" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3082,49 +3082,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R26" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3183,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R27" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R22" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R23" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127126184</v>
+        <v>127127137</v>
       </c>
       <c r="B16" t="n">
         <v>80121</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595844</v>
+        <v>595925</v>
       </c>
       <c r="R16" t="n">
-        <v>6986247</v>
+        <v>6986226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127137</v>
+        <v>127126184</v>
       </c>
       <c r="B17" t="n">
         <v>80121</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595925</v>
+        <v>595844</v>
       </c>
       <c r="R17" t="n">
-        <v>6986226</v>
+        <v>6986247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
         <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R22" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R23" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>91904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R24" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B25" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R25" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3082,45 +3082,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R26" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3179,49 +3183,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R27" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126974</v>
+        <v>127125963</v>
       </c>
       <c r="B9" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,34 +1410,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595916</v>
+        <v>595866</v>
       </c>
       <c r="R9" t="n">
-        <v>6986192</v>
+        <v>6986273</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,38 +1506,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127125963</v>
+        <v>127126832</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1536,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595866</v>
+        <v>595893</v>
       </c>
       <c r="R10" t="n">
-        <v>6986273</v>
+        <v>6986174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1581,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,49 +1607,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126832</v>
+        <v>127126974</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595893</v>
+        <v>595916</v>
       </c>
       <c r="R11" t="n">
-        <v>6986174</v>
+        <v>6986192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3082,49 +3082,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R26" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3183,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R27" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127126594</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R3" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R4" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>127126904</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127126520</v>
+        <v>127126740</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,27 +1201,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595819</v>
+        <v>595917</v>
       </c>
       <c r="R7" t="n">
-        <v>6986191</v>
+        <v>6986144</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B8" t="n">
-        <v>57821</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,27 +1303,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R8" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127125963</v>
+        <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,39 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595866</v>
+        <v>595916</v>
       </c>
       <c r="R9" t="n">
-        <v>6986273</v>
+        <v>6986192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,37 +1496,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126832</v>
+        <v>127125963</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1545,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595893</v>
+        <v>595866</v>
       </c>
       <c r="R10" t="n">
-        <v>6986174</v>
+        <v>6986273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,45 +1603,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126974</v>
+        <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595916</v>
+        <v>595893</v>
       </c>
       <c r="R11" t="n">
-        <v>6986192</v>
+        <v>6986174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,7 +1707,7 @@
         <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97328</v>
+        <v>97330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127127137</v>
+        <v>127126184</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595925</v>
+        <v>595844</v>
       </c>
       <c r="R16" t="n">
-        <v>6986226</v>
+        <v>6986247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127126184</v>
+        <v>127127137</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595844</v>
+        <v>595925</v>
       </c>
       <c r="R17" t="n">
-        <v>6986247</v>
+        <v>6986226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>127127199</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,45 +2387,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127074</v>
+        <v>127124915</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595931</v>
+        <v>595778</v>
       </c>
       <c r="R19" t="n">
-        <v>6986212</v>
+        <v>6986242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,49 +2488,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124915</v>
+        <v>127127074</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>80123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595778</v>
+        <v>595931</v>
       </c>
       <c r="R20" t="n">
-        <v>6986242</v>
+        <v>6986212</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>127126106</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>80123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R22" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>91332</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R23" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2891,7 +2891,7 @@
         <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>127428596</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>127428437</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R3" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R4" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,27 +1201,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R7" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126520</v>
+        <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,27 +1308,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595819</v>
+        <v>595917</v>
       </c>
       <c r="R8" t="n">
-        <v>6986191</v>
+        <v>6986144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2387,49 +2387,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124915</v>
+        <v>127127074</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595778</v>
+        <v>595931</v>
       </c>
       <c r="R19" t="n">
-        <v>6986242</v>
+        <v>6986212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,45 +2484,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127127074</v>
+        <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>80123</v>
+        <v>98367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595931</v>
+        <v>595778</v>
       </c>
       <c r="R20" t="n">
-        <v>6986212</v>
+        <v>6986242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R22" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B23" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R23" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R3" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R4" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,45 +1093,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127127032</v>
+        <v>127126740</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595935</v>
+        <v>595917</v>
       </c>
       <c r="R6" t="n">
-        <v>6986169</v>
+        <v>6986144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,50 +1195,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127126520</v>
+        <v>127127032</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595819</v>
+        <v>595935</v>
       </c>
       <c r="R7" t="n">
-        <v>6986191</v>
+        <v>6986169</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126740</v>
+        <v>127126520</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,27 +1303,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595917</v>
+        <v>595819</v>
       </c>
       <c r="R8" t="n">
-        <v>6986144</v>
+        <v>6986191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R3" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R4" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,50 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127126740</v>
+        <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595917</v>
+        <v>595935</v>
       </c>
       <c r="R6" t="n">
-        <v>6986144</v>
+        <v>6986169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,45 +1190,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127127032</v>
+        <v>127126520</v>
       </c>
       <c r="B7" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595935</v>
+        <v>595819</v>
       </c>
       <c r="R7" t="n">
-        <v>6986169</v>
+        <v>6986191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127126520</v>
+        <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,27 +1308,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595819</v>
+        <v>595917</v>
       </c>
       <c r="R8" t="n">
-        <v>6986191</v>
+        <v>6986144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,7 +1402,7 @@
         <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97330</v>
+        <v>97336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B24" t="n">
-        <v>91906</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R24" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>91912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R25" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3182,7 +3182,7 @@
         <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127126594</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127126227</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127126709</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127126904</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127126520</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>127125963</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97336</v>
+        <v>97339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>127126184</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>127127137</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>127127199</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,45 +2387,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127074</v>
+        <v>127124915</v>
       </c>
       <c r="B19" t="n">
-        <v>80123</v>
+        <v>98376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595931</v>
+        <v>595778</v>
       </c>
       <c r="R19" t="n">
-        <v>6986212</v>
+        <v>6986242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,49 +2488,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124915</v>
+        <v>127127074</v>
       </c>
       <c r="B20" t="n">
-        <v>98373</v>
+        <v>80126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595778</v>
+        <v>595931</v>
       </c>
       <c r="R20" t="n">
-        <v>6986242</v>
+        <v>6986212</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>127126106</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>127428158</v>
       </c>
       <c r="B23" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>127428596</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>127428192</v>
       </c>
       <c r="B25" t="n">
-        <v>91912</v>
+        <v>91915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,45 +3082,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R26" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3179,49 +3183,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R27" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127126594</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127126227</v>
+        <v>127126709</v>
       </c>
       <c r="B3" t="n">
-        <v>80155</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595842</v>
+        <v>595884</v>
       </c>
       <c r="R3" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127126709</v>
+        <v>127126227</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>80161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595884</v>
+        <v>595842</v>
       </c>
       <c r="R4" t="n">
-        <v>6986161</v>
+        <v>6986255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>127126904</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127127032</v>
       </c>
       <c r="B6" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127126520</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127126740</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,45 +1399,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126974</v>
+        <v>127126832</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595916</v>
+        <v>595893</v>
       </c>
       <c r="R9" t="n">
-        <v>6986192</v>
+        <v>6986174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127125963</v>
+        <v>127126974</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,39 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595866</v>
+        <v>595916</v>
       </c>
       <c r="R10" t="n">
-        <v>6986273</v>
+        <v>6986192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,37 +1597,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126832</v>
+        <v>127125963</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595893</v>
+        <v>595866</v>
       </c>
       <c r="R11" t="n">
-        <v>6986174</v>
+        <v>6986273</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,6 +1673,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,7 +1707,7 @@
         <v>127125812</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127126867</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127126969</v>
       </c>
       <c r="B14" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>127126663</v>
       </c>
       <c r="B15" t="n">
-        <v>97339</v>
+        <v>97347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>127126184</v>
       </c>
       <c r="B16" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>127127137</v>
       </c>
       <c r="B17" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>127127199</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>127124915</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>127127074</v>
       </c>
       <c r="B20" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>127126106</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>127428158</v>
       </c>
       <c r="B23" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R24" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B25" t="n">
-        <v>91915</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R25" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3082,49 +3082,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R26" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3183,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R27" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -1399,49 +1399,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127126832</v>
+        <v>127126974</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595893</v>
+        <v>595916</v>
       </c>
       <c r="R9" t="n">
-        <v>6986174</v>
+        <v>6986192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126974</v>
+        <v>127125963</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595916</v>
+        <v>595866</v>
       </c>
       <c r="R10" t="n">
-        <v>6986192</v>
+        <v>6986273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,38 +1603,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125963</v>
+        <v>127126832</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595866</v>
+        <v>595893</v>
       </c>
       <c r="R11" t="n">
-        <v>6986273</v>
+        <v>6986174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,45 +1704,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125812</v>
+        <v>127126867</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595914</v>
+        <v>595892</v>
       </c>
       <c r="R12" t="n">
-        <v>6986314</v>
+        <v>6986187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,49 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126867</v>
+        <v>127125812</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595892</v>
+        <v>595914</v>
       </c>
       <c r="R13" t="n">
-        <v>6986187</v>
+        <v>6986314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2387,49 +2387,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124915</v>
+        <v>127127074</v>
       </c>
       <c r="B19" t="n">
-        <v>98384</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595778</v>
+        <v>595931</v>
       </c>
       <c r="R19" t="n">
-        <v>6986242</v>
+        <v>6986212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,45 +2484,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127127074</v>
+        <v>127124915</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>98384</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595931</v>
+        <v>595778</v>
       </c>
       <c r="R20" t="n">
-        <v>6986212</v>
+        <v>6986242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,7 +2697,7 @@
         <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -2697,7 +2697,7 @@
         <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B24" t="n">
-        <v>91924</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R24" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>91925</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R25" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3182,7 +3182,7 @@
         <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -2697,7 +2697,7 @@
         <v>127428280</v>
       </c>
       <c r="B22" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,32 +2888,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127428596</v>
+        <v>127428192</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>91926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595930</v>
+        <v>595852</v>
       </c>
       <c r="R24" t="n">
-        <v>6986250</v>
+        <v>6986240</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2985,32 +2985,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127428192</v>
+        <v>127428596</v>
       </c>
       <c r="B25" t="n">
-        <v>91925</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595852</v>
+        <v>595930</v>
       </c>
       <c r="R25" t="n">
-        <v>6986240</v>
+        <v>6986250</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3082,45 +3082,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R26" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3179,49 +3183,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R27" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>127428774</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127428280</v>
+        <v>127428158</v>
       </c>
       <c r="B22" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595878</v>
+        <v>595853</v>
       </c>
       <c r="R22" t="n">
-        <v>6986233</v>
+        <v>6986240</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127428158</v>
+        <v>127428280</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595853</v>
+        <v>595878</v>
       </c>
       <c r="R23" t="n">
-        <v>6986240</v>
+        <v>6986233</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3082,49 +3082,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127428567</v>
+        <v>127428437</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595920</v>
+        <v>595915</v>
       </c>
       <c r="R26" t="n">
-        <v>6986240</v>
+        <v>6986247</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3183,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127428437</v>
+        <v>127428567</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högåsen, Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595915</v>
+        <v>595920</v>
       </c>
       <c r="R27" t="n">
-        <v>6986247</v>
+        <v>6986240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3379,6 +3379,455 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129297449</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>MalmÃ¥n, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>595918</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6986234</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ã…tminstone ca 300 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129297446</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92110</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>760</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>595845</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6986257</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129297447</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>595860</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6986205</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129297448</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>MalmÃ¥n, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>595927</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6986176</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3827,6 +3827,741 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129431269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>595884</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6986191</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129431265</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>595985</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6986204</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129431270</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>595846</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6986212</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129431268</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>595884</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6986158</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129431266</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>595868</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6986274</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129431267</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>595930</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6986173</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129431271</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>595815</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6986246</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -4040,7 +4040,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431270</v>
+        <v>129431268</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595846</v>
+        <v>595884</v>
       </c>
       <c r="R35" t="n">
-        <v>6986212</v>
+        <v>6986158</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129431268</v>
+        <v>129431270</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595884</v>
+        <v>595846</v>
       </c>
       <c r="R36" t="n">
-        <v>6986158</v>
+        <v>6986212</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 22986-2025 artfynd.xlsx
+++ b/artfynd/A 22986-2025 artfynd.xlsx
@@ -3384,7 +3384,7 @@
         <v>129297449</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129297446</v>
       </c>
       <c r="B30" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129297447</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129297448</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431268</v>
+        <v>129431270</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595884</v>
+        <v>595846</v>
       </c>
       <c r="R35" t="n">
-        <v>6986158</v>
+        <v>6986212</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129431270</v>
+        <v>129431268</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595846</v>
+        <v>595884</v>
       </c>
       <c r="R36" t="n">
-        <v>6986212</v>
+        <v>6986158</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
